--- a/branches/fix/datasets-entry-stable-target/all-profiles.xlsx
+++ b/branches/fix/datasets-entry-stable-target/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T11:48:31+00:00</t>
+    <t>2026-08-14T11:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
